--- a/artfynd/A 35570-2024 artfynd.xlsx
+++ b/artfynd/A 35570-2024 artfynd.xlsx
@@ -2193,10 +2193,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119678587</v>
+        <v>119678608</v>
       </c>
       <c r="B16" t="n">
-        <v>57310</v>
+        <v>78560</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2209,31 +2209,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2241,10 +2236,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>476435</v>
+        <v>476427</v>
       </c>
       <c r="R16" t="n">
-        <v>6793012</v>
+        <v>6793037</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2285,6 +2280,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2303,10 +2299,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119678608</v>
+        <v>119678587</v>
       </c>
       <c r="B17" t="n">
-        <v>78560</v>
+        <v>57310</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2319,26 +2315,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2346,10 +2347,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>476427</v>
+        <v>476435</v>
       </c>
       <c r="R17" t="n">
-        <v>6793037</v>
+        <v>6793012</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2390,7 +2391,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35570-2024 artfynd.xlsx
+++ b/artfynd/A 35570-2024 artfynd.xlsx
@@ -792,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119526985</v>
+        <v>119527155</v>
       </c>
       <c r="B3" t="n">
         <v>78560</v>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476468</v>
+        <v>476528</v>
       </c>
       <c r="R3" t="n">
-        <v>6793033</v>
+        <v>6793024</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1021,7 +1021,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119527155</v>
+        <v>119526985</v>
       </c>
       <c r="B5" t="n">
         <v>78560</v>
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476528</v>
+        <v>476468</v>
       </c>
       <c r="R5" t="n">
-        <v>6793024</v>
+        <v>6793033</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,7 +1133,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119674326</v>
+        <v>119674187</v>
       </c>
       <c r="B6" t="n">
         <v>78526</v>
@@ -1176,10 +1176,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476503</v>
+        <v>476584</v>
       </c>
       <c r="R6" t="n">
-        <v>6792972</v>
+        <v>6792974</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1239,7 +1239,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119674286</v>
+        <v>119674307</v>
       </c>
       <c r="B7" t="n">
         <v>78526</v>
@@ -1282,10 +1282,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476576</v>
+        <v>476565</v>
       </c>
       <c r="R7" t="n">
-        <v>6792964</v>
+        <v>6792952</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1557,7 +1557,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119674125</v>
+        <v>119674310</v>
       </c>
       <c r="B10" t="n">
         <v>78526</v>
@@ -1600,10 +1600,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476581</v>
+        <v>476541</v>
       </c>
       <c r="R10" t="n">
-        <v>6792984</v>
+        <v>6792948</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1663,7 +1663,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119674310</v>
+        <v>119674277</v>
       </c>
       <c r="B11" t="n">
         <v>78526</v>
@@ -1706,10 +1706,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476541</v>
+        <v>476585</v>
       </c>
       <c r="R11" t="n">
-        <v>6792948</v>
+        <v>6792971</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1769,7 +1769,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119674187</v>
+        <v>119674326</v>
       </c>
       <c r="B12" t="n">
         <v>78526</v>
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476584</v>
+        <v>476503</v>
       </c>
       <c r="R12" t="n">
-        <v>6792974</v>
+        <v>6792972</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1875,7 +1875,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119674277</v>
+        <v>119674076</v>
       </c>
       <c r="B13" t="n">
         <v>78526</v>
@@ -1914,14 +1914,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Unnån-Mysingen, Dlr</t>
+          <t>Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476585</v>
+        <v>476581</v>
       </c>
       <c r="R13" t="n">
-        <v>6792971</v>
+        <v>6792984</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1981,7 +1981,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119674307</v>
+        <v>119674286</v>
       </c>
       <c r="B14" t="n">
         <v>78526</v>
@@ -2024,10 +2024,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>476565</v>
+        <v>476576</v>
       </c>
       <c r="R14" t="n">
-        <v>6792952</v>
+        <v>6792964</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2193,10 +2193,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119678608</v>
+        <v>119678675</v>
       </c>
       <c r="B16" t="n">
-        <v>78560</v>
+        <v>78526</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2209,21 +2209,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2236,10 +2236,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>476427</v>
+        <v>476462</v>
       </c>
       <c r="R16" t="n">
-        <v>6793037</v>
+        <v>6793057</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2299,10 +2299,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119678587</v>
+        <v>119678669</v>
       </c>
       <c r="B17" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2315,31 +2315,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2347,10 +2342,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>476435</v>
+        <v>476451</v>
       </c>
       <c r="R17" t="n">
-        <v>6793012</v>
+        <v>6793064</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2391,6 +2386,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2409,7 +2405,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119678669</v>
+        <v>119678543</v>
       </c>
       <c r="B18" t="n">
         <v>78526</v>
@@ -2452,10 +2448,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>476451</v>
+        <v>476496</v>
       </c>
       <c r="R18" t="n">
-        <v>6793064</v>
+        <v>6792985</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2515,7 +2511,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119678775</v>
+        <v>119678809</v>
       </c>
       <c r="B19" t="n">
         <v>78526</v>
@@ -2558,10 +2554,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>476576</v>
+        <v>476580</v>
       </c>
       <c r="R19" t="n">
-        <v>6793002</v>
+        <v>6793009</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2621,7 +2617,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119678809</v>
+        <v>119678773</v>
       </c>
       <c r="B20" t="n">
         <v>78526</v>
@@ -2664,10 +2660,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>476580</v>
+        <v>476572</v>
       </c>
       <c r="R20" t="n">
-        <v>6793009</v>
+        <v>6793012</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2727,10 +2723,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119678650</v>
+        <v>119678589</v>
       </c>
       <c r="B21" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2743,26 +2739,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2770,10 +2771,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>476426</v>
+        <v>476438</v>
       </c>
       <c r="R21" t="n">
-        <v>6793060</v>
+        <v>6793022</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2814,7 +2815,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2833,7 +2833,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119678764</v>
+        <v>119678593</v>
       </c>
       <c r="B22" t="n">
         <v>78526</v>
@@ -2876,10 +2876,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>476546</v>
+        <v>476443</v>
       </c>
       <c r="R22" t="n">
-        <v>6793032</v>
+        <v>6793023</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2939,7 +2939,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119678675</v>
+        <v>119678650</v>
       </c>
       <c r="B23" t="n">
         <v>78526</v>
@@ -2982,10 +2982,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>476462</v>
+        <v>476426</v>
       </c>
       <c r="R23" t="n">
-        <v>6793057</v>
+        <v>6793060</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3045,7 +3045,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119678681</v>
+        <v>119678775</v>
       </c>
       <c r="B24" t="n">
         <v>78526</v>
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>476465</v>
+        <v>476576</v>
       </c>
       <c r="R24" t="n">
-        <v>6793055</v>
+        <v>6793002</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3151,10 +3151,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119678593</v>
+        <v>119678608</v>
       </c>
       <c r="B25" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3167,21 +3167,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3194,10 +3194,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>476443</v>
+        <v>476427</v>
       </c>
       <c r="R25" t="n">
-        <v>6793023</v>
+        <v>6793037</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3257,7 +3257,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119678611</v>
+        <v>119678605</v>
       </c>
       <c r="B26" t="n">
         <v>78526</v>
@@ -3300,10 +3300,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>476432</v>
+        <v>476435</v>
       </c>
       <c r="R26" t="n">
-        <v>6793036</v>
+        <v>6793041</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3363,10 +3363,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119678768</v>
+        <v>119678679</v>
       </c>
       <c r="B27" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3379,21 +3379,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3406,10 +3406,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>476545</v>
+        <v>476461</v>
       </c>
       <c r="R27" t="n">
-        <v>6793032</v>
+        <v>6793055</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3469,7 +3469,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119678773</v>
+        <v>119678685</v>
       </c>
       <c r="B28" t="n">
         <v>78526</v>
@@ -3512,10 +3512,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>476572</v>
+        <v>476473</v>
       </c>
       <c r="R28" t="n">
-        <v>6793012</v>
+        <v>6793064</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3575,7 +3575,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119678688</v>
+        <v>119678552</v>
       </c>
       <c r="B29" t="n">
         <v>78526</v>
@@ -3618,10 +3618,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>476483</v>
+        <v>476498</v>
       </c>
       <c r="R29" t="n">
-        <v>6793080</v>
+        <v>6792989</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3681,7 +3681,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119678624</v>
+        <v>119678611</v>
       </c>
       <c r="B30" t="n">
         <v>78526</v>
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>476413</v>
+        <v>476432</v>
       </c>
       <c r="R30" t="n">
-        <v>6793054</v>
+        <v>6793036</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3787,10 +3787,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119678743</v>
+        <v>119678688</v>
       </c>
       <c r="B31" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3799,37 +3799,29 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
@@ -3838,10 +3830,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>476514</v>
+        <v>476483</v>
       </c>
       <c r="R31" t="n">
-        <v>6793070</v>
+        <v>6793080</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3901,10 +3893,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119678618</v>
+        <v>119678743</v>
       </c>
       <c r="B32" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3913,29 +3905,37 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
@@ -3944,10 +3944,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>476427</v>
+        <v>476514</v>
       </c>
       <c r="R32" t="n">
-        <v>6793043</v>
+        <v>6793070</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4007,10 +4007,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119678589</v>
+        <v>119678768</v>
       </c>
       <c r="B33" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4023,31 +4023,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4055,10 +4050,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>476438</v>
+        <v>476545</v>
       </c>
       <c r="R33" t="n">
-        <v>6793022</v>
+        <v>6793032</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4099,6 +4094,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4231,7 +4227,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119678685</v>
+        <v>119678681</v>
       </c>
       <c r="B35" t="n">
         <v>78526</v>
@@ -4274,10 +4270,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>476473</v>
+        <v>476465</v>
       </c>
       <c r="R35" t="n">
-        <v>6793064</v>
+        <v>6793055</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4337,7 +4333,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119678552</v>
+        <v>119678618</v>
       </c>
       <c r="B36" t="n">
         <v>78526</v>
@@ -4380,10 +4376,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>476498</v>
+        <v>476427</v>
       </c>
       <c r="R36" t="n">
-        <v>6792989</v>
+        <v>6793043</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4443,7 +4439,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119678602</v>
+        <v>119678774</v>
       </c>
       <c r="B37" t="n">
         <v>78526</v>
@@ -4486,10 +4482,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>476446</v>
+        <v>476573</v>
       </c>
       <c r="R37" t="n">
-        <v>6793039</v>
+        <v>6793014</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4549,7 +4545,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119678543</v>
+        <v>119678624</v>
       </c>
       <c r="B38" t="n">
         <v>78526</v>
@@ -4592,10 +4588,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>476496</v>
+        <v>476413</v>
       </c>
       <c r="R38" t="n">
-        <v>6792985</v>
+        <v>6793054</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4655,7 +4651,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119678774</v>
+        <v>119678764</v>
       </c>
       <c r="B39" t="n">
         <v>78526</v>
@@ -4698,10 +4694,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>476573</v>
+        <v>476546</v>
       </c>
       <c r="R39" t="n">
-        <v>6793014</v>
+        <v>6793032</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4761,7 +4757,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119678605</v>
+        <v>119678602</v>
       </c>
       <c r="B40" t="n">
         <v>78526</v>
@@ -4804,10 +4800,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>476435</v>
+        <v>476446</v>
       </c>
       <c r="R40" t="n">
-        <v>6793041</v>
+        <v>6793039</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4867,10 +4863,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119678679</v>
+        <v>119678587</v>
       </c>
       <c r="B41" t="n">
-        <v>78560</v>
+        <v>57310</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4883,26 +4879,31 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4910,10 +4911,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>476461</v>
+        <v>476435</v>
       </c>
       <c r="R41" t="n">
-        <v>6793055</v>
+        <v>6793012</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4954,7 +4955,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35570-2024 artfynd.xlsx
+++ b/artfynd/A 35570-2024 artfynd.xlsx
@@ -3893,10 +3893,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119678743</v>
+        <v>119678768</v>
       </c>
       <c r="B32" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3905,37 +3905,29 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
@@ -3944,10 +3936,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>476514</v>
+        <v>476545</v>
       </c>
       <c r="R32" t="n">
-        <v>6793070</v>
+        <v>6793032</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4007,10 +3999,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119678768</v>
+        <v>119678743</v>
       </c>
       <c r="B33" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4019,29 +4011,37 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
@@ -4050,10 +4050,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>476545</v>
+        <v>476514</v>
       </c>
       <c r="R33" t="n">
-        <v>6793032</v>
+        <v>6793070</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>

--- a/artfynd/A 35570-2024 artfynd.xlsx
+++ b/artfynd/A 35570-2024 artfynd.xlsx
@@ -1133,7 +1133,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119674187</v>
+        <v>119674062</v>
       </c>
       <c r="B6" t="n">
         <v>78526</v>
@@ -1176,10 +1176,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476584</v>
+        <v>476579</v>
       </c>
       <c r="R6" t="n">
-        <v>6792974</v>
+        <v>6792992</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1345,7 +1345,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119674299</v>
+        <v>119674310</v>
       </c>
       <c r="B8" t="n">
         <v>78526</v>
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476564</v>
+        <v>476541</v>
       </c>
       <c r="R8" t="n">
-        <v>6792952</v>
+        <v>6792948</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1451,7 +1451,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119674324</v>
+        <v>119674076</v>
       </c>
       <c r="B9" t="n">
         <v>78526</v>
@@ -1490,14 +1490,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Unnån-Mysingen, Dlr</t>
+          <t>Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>476507</v>
+        <v>476581</v>
       </c>
       <c r="R9" t="n">
-        <v>6792948</v>
+        <v>6792984</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1557,7 +1557,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119674310</v>
+        <v>119674324</v>
       </c>
       <c r="B10" t="n">
         <v>78526</v>
@@ -1600,7 +1600,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476541</v>
+        <v>476507</v>
       </c>
       <c r="R10" t="n">
         <v>6792948</v>
@@ -1663,7 +1663,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119674277</v>
+        <v>119674326</v>
       </c>
       <c r="B11" t="n">
         <v>78526</v>
@@ -1706,10 +1706,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476585</v>
+        <v>476503</v>
       </c>
       <c r="R11" t="n">
-        <v>6792971</v>
+        <v>6792972</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1769,7 +1769,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119674326</v>
+        <v>119674286</v>
       </c>
       <c r="B12" t="n">
         <v>78526</v>
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476503</v>
+        <v>476576</v>
       </c>
       <c r="R12" t="n">
-        <v>6792972</v>
+        <v>6792964</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1875,7 +1875,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119674076</v>
+        <v>119674299</v>
       </c>
       <c r="B13" t="n">
         <v>78526</v>
@@ -1914,14 +1914,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Unnån, Dlr</t>
+          <t>Unnån-Mysingen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476581</v>
+        <v>476564</v>
       </c>
       <c r="R13" t="n">
-        <v>6792984</v>
+        <v>6792952</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1981,7 +1981,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119674286</v>
+        <v>119674277</v>
       </c>
       <c r="B14" t="n">
         <v>78526</v>
@@ -2024,10 +2024,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>476576</v>
+        <v>476585</v>
       </c>
       <c r="R14" t="n">
-        <v>6792964</v>
+        <v>6792971</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2087,7 +2087,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119674062</v>
+        <v>119674187</v>
       </c>
       <c r="B15" t="n">
         <v>78526</v>
@@ -2130,10 +2130,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>476579</v>
+        <v>476584</v>
       </c>
       <c r="R15" t="n">
-        <v>6792992</v>
+        <v>6792974</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2193,7 +2193,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119678675</v>
+        <v>119678624</v>
       </c>
       <c r="B16" t="n">
         <v>78526</v>
@@ -2236,10 +2236,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>476462</v>
+        <v>476413</v>
       </c>
       <c r="R16" t="n">
-        <v>6793057</v>
+        <v>6793054</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2299,7 +2299,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119678669</v>
+        <v>119678593</v>
       </c>
       <c r="B17" t="n">
         <v>78526</v>
@@ -2342,10 +2342,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>476451</v>
+        <v>476443</v>
       </c>
       <c r="R17" t="n">
-        <v>6793064</v>
+        <v>6793023</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2405,10 +2405,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119678543</v>
+        <v>119678737</v>
       </c>
       <c r="B18" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2417,29 +2417,37 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
@@ -2448,10 +2456,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>476496</v>
+        <v>476513</v>
       </c>
       <c r="R18" t="n">
-        <v>6792985</v>
+        <v>6793069</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2511,7 +2519,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119678809</v>
+        <v>119678543</v>
       </c>
       <c r="B19" t="n">
         <v>78526</v>
@@ -2554,10 +2562,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>476580</v>
+        <v>476496</v>
       </c>
       <c r="R19" t="n">
-        <v>6793009</v>
+        <v>6792985</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2617,7 +2625,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119678773</v>
+        <v>119678809</v>
       </c>
       <c r="B20" t="n">
         <v>78526</v>
@@ -2660,10 +2668,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>476572</v>
+        <v>476580</v>
       </c>
       <c r="R20" t="n">
-        <v>6793012</v>
+        <v>6793009</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2723,10 +2731,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119678589</v>
+        <v>119678764</v>
       </c>
       <c r="B21" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2739,31 +2747,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2771,10 +2774,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>476438</v>
+        <v>476546</v>
       </c>
       <c r="R21" t="n">
-        <v>6793022</v>
+        <v>6793032</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2815,6 +2818,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2833,7 +2837,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119678593</v>
+        <v>119678681</v>
       </c>
       <c r="B22" t="n">
         <v>78526</v>
@@ -2876,10 +2880,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>476443</v>
+        <v>476465</v>
       </c>
       <c r="R22" t="n">
-        <v>6793023</v>
+        <v>6793055</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2939,7 +2943,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119678650</v>
+        <v>119678552</v>
       </c>
       <c r="B23" t="n">
         <v>78526</v>
@@ -2982,10 +2986,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>476426</v>
+        <v>476498</v>
       </c>
       <c r="R23" t="n">
-        <v>6793060</v>
+        <v>6792989</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3045,10 +3049,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119678775</v>
+        <v>119678589</v>
       </c>
       <c r="B24" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3061,26 +3065,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3088,10 +3097,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>476576</v>
+        <v>476438</v>
       </c>
       <c r="R24" t="n">
-        <v>6793002</v>
+        <v>6793022</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3132,7 +3141,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3151,10 +3159,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119678608</v>
+        <v>119678611</v>
       </c>
       <c r="B25" t="n">
-        <v>78560</v>
+        <v>78526</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3167,21 +3175,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3194,10 +3202,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>476427</v>
+        <v>476432</v>
       </c>
       <c r="R25" t="n">
-        <v>6793037</v>
+        <v>6793036</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3257,7 +3265,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119678605</v>
+        <v>119678775</v>
       </c>
       <c r="B26" t="n">
         <v>78526</v>
@@ -3300,10 +3308,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>476435</v>
+        <v>476576</v>
       </c>
       <c r="R26" t="n">
-        <v>6793041</v>
+        <v>6793002</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3363,7 +3371,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119678679</v>
+        <v>119678608</v>
       </c>
       <c r="B27" t="n">
         <v>78560</v>
@@ -3406,10 +3414,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>476461</v>
+        <v>476427</v>
       </c>
       <c r="R27" t="n">
-        <v>6793055</v>
+        <v>6793037</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3469,10 +3477,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119678685</v>
+        <v>119678743</v>
       </c>
       <c r="B28" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3481,29 +3489,37 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
@@ -3512,10 +3528,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>476473</v>
+        <v>476514</v>
       </c>
       <c r="R28" t="n">
-        <v>6793064</v>
+        <v>6793070</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3575,7 +3591,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119678552</v>
+        <v>119678605</v>
       </c>
       <c r="B29" t="n">
         <v>78526</v>
@@ -3618,10 +3634,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>476498</v>
+        <v>476435</v>
       </c>
       <c r="R29" t="n">
-        <v>6792989</v>
+        <v>6793041</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3681,7 +3697,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119678611</v>
+        <v>119678685</v>
       </c>
       <c r="B30" t="n">
         <v>78526</v>
@@ -3724,10 +3740,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>476432</v>
+        <v>476473</v>
       </c>
       <c r="R30" t="n">
-        <v>6793036</v>
+        <v>6793064</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3999,10 +4015,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119678743</v>
+        <v>119678650</v>
       </c>
       <c r="B33" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4011,37 +4027,29 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
@@ -4050,10 +4058,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>476514</v>
+        <v>476426</v>
       </c>
       <c r="R33" t="n">
-        <v>6793070</v>
+        <v>6793060</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4113,10 +4121,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119678737</v>
+        <v>119678602</v>
       </c>
       <c r="B34" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4125,37 +4133,29 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
@@ -4164,10 +4164,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>476513</v>
+        <v>476446</v>
       </c>
       <c r="R34" t="n">
-        <v>6793069</v>
+        <v>6793039</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4227,7 +4227,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119678681</v>
+        <v>119678773</v>
       </c>
       <c r="B35" t="n">
         <v>78526</v>
@@ -4270,10 +4270,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>476465</v>
+        <v>476572</v>
       </c>
       <c r="R35" t="n">
-        <v>6793055</v>
+        <v>6793012</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4333,7 +4333,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119678618</v>
+        <v>119678669</v>
       </c>
       <c r="B36" t="n">
         <v>78526</v>
@@ -4376,10 +4376,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>476427</v>
+        <v>476451</v>
       </c>
       <c r="R36" t="n">
-        <v>6793043</v>
+        <v>6793064</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4545,10 +4545,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119678624</v>
+        <v>119678679</v>
       </c>
       <c r="B38" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4561,21 +4561,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4588,10 +4588,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>476413</v>
+        <v>476461</v>
       </c>
       <c r="R38" t="n">
-        <v>6793054</v>
+        <v>6793055</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4651,10 +4651,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119678764</v>
+        <v>119678587</v>
       </c>
       <c r="B39" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4667,26 +4667,31 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4694,10 +4699,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>476546</v>
+        <v>476435</v>
       </c>
       <c r="R39" t="n">
-        <v>6793032</v>
+        <v>6793012</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4738,7 +4743,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4757,7 +4761,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119678602</v>
+        <v>119678675</v>
       </c>
       <c r="B40" t="n">
         <v>78526</v>
@@ -4800,10 +4804,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>476446</v>
+        <v>476462</v>
       </c>
       <c r="R40" t="n">
-        <v>6793039</v>
+        <v>6793057</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4863,10 +4867,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119678587</v>
+        <v>119678618</v>
       </c>
       <c r="B41" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4879,31 +4883,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4911,10 +4910,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>476435</v>
+        <v>476427</v>
       </c>
       <c r="R41" t="n">
-        <v>6793012</v>
+        <v>6793043</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4955,6 +4954,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35570-2024 artfynd.xlsx
+++ b/artfynd/A 35570-2024 artfynd.xlsx
@@ -2405,10 +2405,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119678737</v>
+        <v>119678543</v>
       </c>
       <c r="B18" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2417,37 +2417,29 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
@@ -2456,10 +2448,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>476513</v>
+        <v>476496</v>
       </c>
       <c r="R18" t="n">
-        <v>6793069</v>
+        <v>6792985</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2519,10 +2511,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119678543</v>
+        <v>119678737</v>
       </c>
       <c r="B19" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2531,29 +2523,37 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
@@ -2562,10 +2562,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>476496</v>
+        <v>476513</v>
       </c>
       <c r="R19" t="n">
-        <v>6792985</v>
+        <v>6793069</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>

--- a/artfynd/A 35570-2024 artfynd.xlsx
+++ b/artfynd/A 35570-2024 artfynd.xlsx
@@ -1239,7 +1239,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119674307</v>
+        <v>119674076</v>
       </c>
       <c r="B7" t="n">
         <v>78526</v>
@@ -1278,14 +1278,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Unnån-Mysingen, Dlr</t>
+          <t>Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476565</v>
+        <v>476581</v>
       </c>
       <c r="R7" t="n">
-        <v>6792952</v>
+        <v>6792984</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1345,7 +1345,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119674310</v>
+        <v>119674187</v>
       </c>
       <c r="B8" t="n">
         <v>78526</v>
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476541</v>
+        <v>476584</v>
       </c>
       <c r="R8" t="n">
-        <v>6792948</v>
+        <v>6792974</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1451,7 +1451,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119674076</v>
+        <v>119674310</v>
       </c>
       <c r="B9" t="n">
         <v>78526</v>
@@ -1490,14 +1490,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Unnån, Dlr</t>
+          <t>Unnån-Mysingen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>476581</v>
+        <v>476541</v>
       </c>
       <c r="R9" t="n">
-        <v>6792984</v>
+        <v>6792948</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1557,7 +1557,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119674324</v>
+        <v>119674286</v>
       </c>
       <c r="B10" t="n">
         <v>78526</v>
@@ -1600,10 +1600,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476507</v>
+        <v>476576</v>
       </c>
       <c r="R10" t="n">
-        <v>6792948</v>
+        <v>6792964</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1663,7 +1663,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119674326</v>
+        <v>119674324</v>
       </c>
       <c r="B11" t="n">
         <v>78526</v>
@@ -1706,10 +1706,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476503</v>
+        <v>476507</v>
       </c>
       <c r="R11" t="n">
-        <v>6792972</v>
+        <v>6792948</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1769,7 +1769,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119674286</v>
+        <v>119674299</v>
       </c>
       <c r="B12" t="n">
         <v>78526</v>
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476576</v>
+        <v>476564</v>
       </c>
       <c r="R12" t="n">
-        <v>6792964</v>
+        <v>6792952</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1875,7 +1875,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119674299</v>
+        <v>119674307</v>
       </c>
       <c r="B13" t="n">
         <v>78526</v>
@@ -1918,7 +1918,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476564</v>
+        <v>476565</v>
       </c>
       <c r="R13" t="n">
         <v>6792952</v>
@@ -2087,7 +2087,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119674187</v>
+        <v>119674326</v>
       </c>
       <c r="B15" t="n">
         <v>78526</v>
@@ -2130,10 +2130,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>476584</v>
+        <v>476503</v>
       </c>
       <c r="R15" t="n">
-        <v>6792974</v>
+        <v>6792972</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2299,7 +2299,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119678593</v>
+        <v>119678552</v>
       </c>
       <c r="B17" t="n">
         <v>78526</v>
@@ -2342,10 +2342,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>476443</v>
+        <v>476498</v>
       </c>
       <c r="R17" t="n">
-        <v>6793023</v>
+        <v>6792989</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2405,7 +2405,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119678543</v>
+        <v>119678675</v>
       </c>
       <c r="B18" t="n">
         <v>78526</v>
@@ -2448,10 +2448,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>476496</v>
+        <v>476462</v>
       </c>
       <c r="R18" t="n">
-        <v>6792985</v>
+        <v>6793057</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119678737</v>
+        <v>119678650</v>
       </c>
       <c r="B19" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2523,37 +2523,29 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
@@ -2562,10 +2554,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>476513</v>
+        <v>476426</v>
       </c>
       <c r="R19" t="n">
-        <v>6793069</v>
+        <v>6793060</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2625,7 +2617,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119678809</v>
+        <v>119678605</v>
       </c>
       <c r="B20" t="n">
         <v>78526</v>
@@ -2668,10 +2660,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>476580</v>
+        <v>476435</v>
       </c>
       <c r="R20" t="n">
-        <v>6793009</v>
+        <v>6793041</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2731,7 +2723,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119678764</v>
+        <v>119678775</v>
       </c>
       <c r="B21" t="n">
         <v>78526</v>
@@ -2774,10 +2766,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>476546</v>
+        <v>476576</v>
       </c>
       <c r="R21" t="n">
-        <v>6793032</v>
+        <v>6793002</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2837,7 +2829,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119678681</v>
+        <v>119678688</v>
       </c>
       <c r="B22" t="n">
         <v>78526</v>
@@ -2880,10 +2872,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>476465</v>
+        <v>476483</v>
       </c>
       <c r="R22" t="n">
-        <v>6793055</v>
+        <v>6793080</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2943,7 +2935,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119678552</v>
+        <v>119678618</v>
       </c>
       <c r="B23" t="n">
         <v>78526</v>
@@ -2986,10 +2978,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>476498</v>
+        <v>476427</v>
       </c>
       <c r="R23" t="n">
-        <v>6792989</v>
+        <v>6793043</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3049,10 +3041,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119678589</v>
+        <v>119678611</v>
       </c>
       <c r="B24" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3065,31 +3057,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3097,10 +3084,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>476438</v>
+        <v>476432</v>
       </c>
       <c r="R24" t="n">
-        <v>6793022</v>
+        <v>6793036</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3141,6 +3128,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3159,10 +3147,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119678611</v>
+        <v>119678608</v>
       </c>
       <c r="B25" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3175,21 +3163,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3202,10 +3190,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>476432</v>
+        <v>476427</v>
       </c>
       <c r="R25" t="n">
-        <v>6793036</v>
+        <v>6793037</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3265,10 +3253,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119678775</v>
+        <v>119678679</v>
       </c>
       <c r="B26" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3281,21 +3269,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3308,10 +3296,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>476576</v>
+        <v>476461</v>
       </c>
       <c r="R26" t="n">
-        <v>6793002</v>
+        <v>6793055</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3371,10 +3359,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119678608</v>
+        <v>119678809</v>
       </c>
       <c r="B27" t="n">
-        <v>78560</v>
+        <v>78526</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3387,21 +3375,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3414,10 +3402,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>476427</v>
+        <v>476580</v>
       </c>
       <c r="R27" t="n">
-        <v>6793037</v>
+        <v>6793009</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3477,10 +3465,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119678743</v>
+        <v>119678774</v>
       </c>
       <c r="B28" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3489,37 +3477,29 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
@@ -3528,10 +3508,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>476514</v>
+        <v>476573</v>
       </c>
       <c r="R28" t="n">
-        <v>6793070</v>
+        <v>6793014</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3591,10 +3571,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119678605</v>
+        <v>119678589</v>
       </c>
       <c r="B29" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3607,26 +3587,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3634,10 +3619,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>476435</v>
+        <v>476438</v>
       </c>
       <c r="R29" t="n">
-        <v>6793041</v>
+        <v>6793022</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3678,7 +3663,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3697,10 +3681,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119678685</v>
+        <v>119678737</v>
       </c>
       <c r="B30" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3709,29 +3693,37 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
@@ -3740,10 +3732,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>476473</v>
+        <v>476513</v>
       </c>
       <c r="R30" t="n">
-        <v>6793064</v>
+        <v>6793069</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3803,7 +3795,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119678688</v>
+        <v>119678685</v>
       </c>
       <c r="B31" t="n">
         <v>78526</v>
@@ -3846,10 +3838,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>476483</v>
+        <v>476473</v>
       </c>
       <c r="R31" t="n">
-        <v>6793080</v>
+        <v>6793064</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3909,7 +3901,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119678768</v>
+        <v>119678681</v>
       </c>
       <c r="B32" t="n">
         <v>78526</v>
@@ -3952,10 +3944,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>476545</v>
+        <v>476465</v>
       </c>
       <c r="R32" t="n">
-        <v>6793032</v>
+        <v>6793055</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4015,10 +4007,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119678650</v>
+        <v>119678587</v>
       </c>
       <c r="B33" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4031,26 +4023,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4058,10 +4055,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>476426</v>
+        <v>476435</v>
       </c>
       <c r="R33" t="n">
-        <v>6793060</v>
+        <v>6793012</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4102,7 +4099,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4121,7 +4117,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119678602</v>
+        <v>119678669</v>
       </c>
       <c r="B34" t="n">
         <v>78526</v>
@@ -4164,10 +4160,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>476446</v>
+        <v>476451</v>
       </c>
       <c r="R34" t="n">
-        <v>6793039</v>
+        <v>6793064</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4227,7 +4223,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119678773</v>
+        <v>119678593</v>
       </c>
       <c r="B35" t="n">
         <v>78526</v>
@@ -4270,10 +4266,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>476572</v>
+        <v>476443</v>
       </c>
       <c r="R35" t="n">
-        <v>6793012</v>
+        <v>6793023</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4333,7 +4329,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119678669</v>
+        <v>119678543</v>
       </c>
       <c r="B36" t="n">
         <v>78526</v>
@@ -4376,10 +4372,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>476451</v>
+        <v>476496</v>
       </c>
       <c r="R36" t="n">
-        <v>6793064</v>
+        <v>6792985</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4439,7 +4435,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119678774</v>
+        <v>119678768</v>
       </c>
       <c r="B37" t="n">
         <v>78526</v>
@@ -4482,10 +4478,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>476573</v>
+        <v>476545</v>
       </c>
       <c r="R37" t="n">
-        <v>6793014</v>
+        <v>6793032</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4545,10 +4541,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119678679</v>
+        <v>119678602</v>
       </c>
       <c r="B38" t="n">
-        <v>78560</v>
+        <v>78526</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4561,21 +4557,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4588,10 +4584,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>476461</v>
+        <v>476446</v>
       </c>
       <c r="R38" t="n">
-        <v>6793055</v>
+        <v>6793039</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4651,10 +4647,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119678587</v>
+        <v>119678743</v>
       </c>
       <c r="B39" t="n">
-        <v>57310</v>
+        <v>91840</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4663,35 +4659,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4699,10 +4698,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>476435</v>
+        <v>476514</v>
       </c>
       <c r="R39" t="n">
-        <v>6793012</v>
+        <v>6793070</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4743,6 +4742,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4761,7 +4761,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119678675</v>
+        <v>119678764</v>
       </c>
       <c r="B40" t="n">
         <v>78526</v>
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>476462</v>
+        <v>476546</v>
       </c>
       <c r="R40" t="n">
-        <v>6793057</v>
+        <v>6793032</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4867,7 +4867,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119678618</v>
+        <v>119678773</v>
       </c>
       <c r="B41" t="n">
         <v>78526</v>
@@ -4910,10 +4910,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>476427</v>
+        <v>476572</v>
       </c>
       <c r="R41" t="n">
-        <v>6793043</v>
+        <v>6793012</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>

--- a/artfynd/A 35570-2024 artfynd.xlsx
+++ b/artfynd/A 35570-2024 artfynd.xlsx
@@ -3147,10 +3147,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119678608</v>
+        <v>119678809</v>
       </c>
       <c r="B25" t="n">
-        <v>78560</v>
+        <v>78526</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3163,21 +3163,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3190,10 +3190,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>476427</v>
+        <v>476580</v>
       </c>
       <c r="R25" t="n">
-        <v>6793037</v>
+        <v>6793009</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3253,10 +3253,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119678679</v>
+        <v>119678774</v>
       </c>
       <c r="B26" t="n">
-        <v>78560</v>
+        <v>78526</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3269,21 +3269,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>476461</v>
+        <v>476573</v>
       </c>
       <c r="R26" t="n">
-        <v>6793055</v>
+        <v>6793014</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3359,10 +3359,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119678809</v>
+        <v>119678608</v>
       </c>
       <c r="B27" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3375,21 +3375,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3402,10 +3402,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>476580</v>
+        <v>476427</v>
       </c>
       <c r="R27" t="n">
-        <v>6793009</v>
+        <v>6793037</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3465,10 +3465,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119678774</v>
+        <v>119678679</v>
       </c>
       <c r="B28" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3481,21 +3481,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3508,10 +3508,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>476573</v>
+        <v>476461</v>
       </c>
       <c r="R28" t="n">
-        <v>6793014</v>
+        <v>6793055</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>

--- a/artfynd/A 35570-2024 artfynd.xlsx
+++ b/artfynd/A 35570-2024 artfynd.xlsx
@@ -3681,10 +3681,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119678737</v>
+        <v>119678685</v>
       </c>
       <c r="B30" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3693,37 +3693,29 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
@@ -3732,10 +3724,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>476513</v>
+        <v>476473</v>
       </c>
       <c r="R30" t="n">
-        <v>6793069</v>
+        <v>6793064</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3795,10 +3787,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119678685</v>
+        <v>119678737</v>
       </c>
       <c r="B31" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3807,29 +3799,37 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
@@ -3838,10 +3838,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>476473</v>
+        <v>476513</v>
       </c>
       <c r="R31" t="n">
-        <v>6793064</v>
+        <v>6793069</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>

--- a/artfynd/A 35570-2024 artfynd.xlsx
+++ b/artfynd/A 35570-2024 artfynd.xlsx
@@ -3681,10 +3681,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119678685</v>
+        <v>119678737</v>
       </c>
       <c r="B30" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3693,29 +3693,37 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
@@ -3724,10 +3732,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>476473</v>
+        <v>476513</v>
       </c>
       <c r="R30" t="n">
-        <v>6793064</v>
+        <v>6793069</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3787,10 +3795,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119678737</v>
+        <v>119678685</v>
       </c>
       <c r="B31" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3799,37 +3807,29 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
@@ -3838,10 +3838,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>476513</v>
+        <v>476473</v>
       </c>
       <c r="R31" t="n">
-        <v>6793069</v>
+        <v>6793064</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>

--- a/artfynd/A 35570-2024 artfynd.xlsx
+++ b/artfynd/A 35570-2024 artfynd.xlsx
@@ -3574,7 +3574,7 @@
         <v>119678589</v>
       </c>
       <c r="B29" t="n">
-        <v>57310</v>
+        <v>57478</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>119678587</v>
       </c>
       <c r="B33" t="n">
-        <v>57310</v>
+        <v>57478</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>

--- a/artfynd/A 35570-2024 artfynd.xlsx
+++ b/artfynd/A 35570-2024 artfynd.xlsx
@@ -3574,7 +3574,7 @@
         <v>119678589</v>
       </c>
       <c r="B29" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>119678587</v>
       </c>
       <c r="B33" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>

--- a/artfynd/A 35570-2024 artfynd.xlsx
+++ b/artfynd/A 35570-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AY47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119527006</v>
+        <v>119526985</v>
       </c>
       <c r="B2" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>476520</v>
+        <v>476468</v>
       </c>
       <c r="R2" t="n">
-        <v>6793006</v>
+        <v>6793033</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:05</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikl</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,12 +785,7 @@
         <v>119527155</v>
       </c>
       <c r="B3" t="n">
-        <v>78560</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,15 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119527031</v>
+        <v>119678608</v>
       </c>
       <c r="B4" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,42 +900,40 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mysingen, Mysingen, Dlr</t>
+          <t>Unnån-Mysingen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476497</v>
+        <v>476427</v>
       </c>
       <c r="R4" t="n">
-        <v>6793060</v>
+        <v>6793037</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,22 +957,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>17:07</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>17:07</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,6 +971,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1021,15 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119526985</v>
+        <v>119678679</v>
       </c>
       <c r="B5" t="n">
-        <v>78560</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1055,19 +1019,22 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mysingen, Mysingen, Dlr</t>
+          <t>Unnån-Mysingen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476468</v>
+        <v>476461</v>
       </c>
       <c r="R5" t="n">
-        <v>6793033</v>
+        <v>6793055</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,22 +1058,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>17:04</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>17:04</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,6 +1072,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1133,15 +1091,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119674062</v>
+        <v>119678737</v>
       </c>
       <c r="B6" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1149,25 +1102,33 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1176,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476579</v>
+        <v>476513</v>
       </c>
       <c r="R6" t="n">
-        <v>6792992</v>
+        <v>6793069</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1239,15 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119674076</v>
+        <v>119678743</v>
       </c>
       <c r="B7" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1255,37 +1211,45 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Unnån, Dlr</t>
+          <t>Unnån-Mysingen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476581</v>
+        <v>476514</v>
       </c>
       <c r="R7" t="n">
-        <v>6792984</v>
+        <v>6793070</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1345,19 +1309,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119674187</v>
+        <v>119526602</v>
       </c>
       <c r="B8" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1379,22 +1338,19 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Unnån-Mysingen, Dlr</t>
+          <t>Mysingen, Mysingen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476584</v>
+        <v>476605</v>
       </c>
       <c r="R8" t="n">
-        <v>6792974</v>
+        <v>6792983</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1418,12 +1374,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:42</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikl</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,7 +1403,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1451,19 +1421,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119674310</v>
+        <v>119527006</v>
       </c>
       <c r="B9" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1485,22 +1450,19 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Unnån-Mysingen, Dlr</t>
+          <t>Mysingen, Mysingen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>476541</v>
+        <v>476520</v>
       </c>
       <c r="R9" t="n">
-        <v>6792948</v>
+        <v>6793006</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1524,12 +1486,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikl</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1538,7 +1515,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1557,19 +1533,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119674286</v>
+        <v>119527031</v>
       </c>
       <c r="B10" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1591,22 +1562,24 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Unnån-Mysingen, Dlr</t>
+          <t>Mysingen, Mysingen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476576</v>
+        <v>476497</v>
       </c>
       <c r="R10" t="n">
-        <v>6792964</v>
+        <v>6793060</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1630,12 +1603,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1644,7 +1627,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1663,19 +1645,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119674324</v>
+        <v>119674062</v>
       </c>
       <c r="B11" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1706,10 +1683,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476507</v>
+        <v>476579</v>
       </c>
       <c r="R11" t="n">
-        <v>6792948</v>
+        <v>6792992</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1769,19 +1746,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119674299</v>
+        <v>119674076</v>
       </c>
       <c r="B12" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1808,14 +1780,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Unnån-Mysingen, Dlr</t>
+          <t>Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476564</v>
+        <v>476581</v>
       </c>
       <c r="R12" t="n">
-        <v>6792952</v>
+        <v>6792984</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1875,19 +1847,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119674307</v>
+        <v>119674187</v>
       </c>
       <c r="B13" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1918,10 +1885,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476565</v>
+        <v>476584</v>
       </c>
       <c r="R13" t="n">
-        <v>6792952</v>
+        <v>6792974</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1984,16 +1951,11 @@
         <v>119674277</v>
       </c>
       <c r="B14" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2087,19 +2049,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119674326</v>
+        <v>119674286</v>
       </c>
       <c r="B15" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2130,10 +2087,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>476503</v>
+        <v>476576</v>
       </c>
       <c r="R15" t="n">
-        <v>6792972</v>
+        <v>6792964</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2193,19 +2150,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119678624</v>
+        <v>119674299</v>
       </c>
       <c r="B16" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2236,10 +2188,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>476413</v>
+        <v>476564</v>
       </c>
       <c r="R16" t="n">
-        <v>6793054</v>
+        <v>6792952</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2299,19 +2251,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119678552</v>
+        <v>119674307</v>
       </c>
       <c r="B17" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2342,10 +2289,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>476498</v>
+        <v>476565</v>
       </c>
       <c r="R17" t="n">
-        <v>6792989</v>
+        <v>6792952</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2405,19 +2352,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119678675</v>
+        <v>119674310</v>
       </c>
       <c r="B18" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2448,10 +2390,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>476462</v>
+        <v>476541</v>
       </c>
       <c r="R18" t="n">
-        <v>6793057</v>
+        <v>6792948</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2511,19 +2453,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119678650</v>
+        <v>119674324</v>
       </c>
       <c r="B19" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2554,10 +2491,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>476426</v>
+        <v>476507</v>
       </c>
       <c r="R19" t="n">
-        <v>6793060</v>
+        <v>6792948</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2617,19 +2554,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119678605</v>
+        <v>119674326</v>
       </c>
       <c r="B20" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2660,10 +2592,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>476435</v>
+        <v>476503</v>
       </c>
       <c r="R20" t="n">
-        <v>6793041</v>
+        <v>6792972</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2723,19 +2655,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119678775</v>
+        <v>119678543</v>
       </c>
       <c r="B21" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2766,10 +2693,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>476576</v>
+        <v>476496</v>
       </c>
       <c r="R21" t="n">
-        <v>6793002</v>
+        <v>6792985</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2829,19 +2756,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119678688</v>
+        <v>119678552</v>
       </c>
       <c r="B22" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2872,10 +2794,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>476483</v>
+        <v>476498</v>
       </c>
       <c r="R22" t="n">
-        <v>6793080</v>
+        <v>6792989</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2935,19 +2857,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119678618</v>
+        <v>119678593</v>
       </c>
       <c r="B23" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2978,10 +2895,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>476427</v>
+        <v>476443</v>
       </c>
       <c r="R23" t="n">
-        <v>6793043</v>
+        <v>6793023</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3041,19 +2958,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119678611</v>
+        <v>119678602</v>
       </c>
       <c r="B24" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3084,10 +2996,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>476432</v>
+        <v>476446</v>
       </c>
       <c r="R24" t="n">
-        <v>6793036</v>
+        <v>6793039</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3147,19 +3059,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119678809</v>
+        <v>119678605</v>
       </c>
       <c r="B25" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3190,10 +3097,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>476580</v>
+        <v>476435</v>
       </c>
       <c r="R25" t="n">
-        <v>6793009</v>
+        <v>6793041</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3253,19 +3160,14 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119678774</v>
+        <v>119678611</v>
       </c>
       <c r="B26" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3296,10 +3198,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>476573</v>
+        <v>476432</v>
       </c>
       <c r="R26" t="n">
-        <v>6793014</v>
+        <v>6793036</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3359,37 +3261,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119678608</v>
+        <v>119678618</v>
       </c>
       <c r="B27" t="n">
-        <v>78560</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3405,7 +3302,7 @@
         <v>476427</v>
       </c>
       <c r="R27" t="n">
-        <v>6793037</v>
+        <v>6793043</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3465,37 +3362,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119678679</v>
+        <v>119678624</v>
       </c>
       <c r="B28" t="n">
-        <v>78560</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3508,10 +3400,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>476461</v>
+        <v>476413</v>
       </c>
       <c r="R28" t="n">
-        <v>6793055</v>
+        <v>6793054</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3571,47 +3463,37 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119678589</v>
+        <v>119678641</v>
       </c>
       <c r="B29" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3619,10 +3501,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>476438</v>
+        <v>476415</v>
       </c>
       <c r="R29" t="n">
-        <v>6793022</v>
+        <v>6793062</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3663,6 +3545,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3681,49 +3564,36 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119678737</v>
+        <v>119678648</v>
       </c>
       <c r="B30" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
@@ -3732,10 +3602,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>476513</v>
+        <v>476424</v>
       </c>
       <c r="R30" t="n">
-        <v>6793069</v>
+        <v>6793061</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3795,19 +3665,14 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119678685</v>
+        <v>119678650</v>
       </c>
       <c r="B31" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -3838,10 +3703,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>476473</v>
+        <v>476426</v>
       </c>
       <c r="R31" t="n">
-        <v>6793064</v>
+        <v>6793060</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3901,19 +3766,14 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119678681</v>
+        <v>119678653</v>
       </c>
       <c r="B32" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -3944,10 +3804,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>476465</v>
+        <v>476431</v>
       </c>
       <c r="R32" t="n">
-        <v>6793055</v>
+        <v>6793065</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4007,47 +3867,37 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119678587</v>
+        <v>119678656</v>
       </c>
       <c r="B33" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4055,10 +3905,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>476435</v>
+        <v>476437</v>
       </c>
       <c r="R33" t="n">
-        <v>6793012</v>
+        <v>6793068</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4099,6 +3949,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4117,19 +3968,14 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119678669</v>
+        <v>119678663</v>
       </c>
       <c r="B34" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -4160,10 +4006,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>476451</v>
+        <v>476437</v>
       </c>
       <c r="R34" t="n">
-        <v>6793064</v>
+        <v>6793067</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4223,19 +4069,14 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119678593</v>
+        <v>119678669</v>
       </c>
       <c r="B35" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4266,10 +4107,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>476443</v>
+        <v>476451</v>
       </c>
       <c r="R35" t="n">
-        <v>6793023</v>
+        <v>6793064</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4329,19 +4170,14 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119678543</v>
+        <v>119678675</v>
       </c>
       <c r="B36" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -4372,10 +4208,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>476496</v>
+        <v>476462</v>
       </c>
       <c r="R36" t="n">
-        <v>6792985</v>
+        <v>6793057</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4435,19 +4271,14 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119678768</v>
+        <v>119678681</v>
       </c>
       <c r="B37" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -4478,10 +4309,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>476545</v>
+        <v>476465</v>
       </c>
       <c r="R37" t="n">
-        <v>6793032</v>
+        <v>6793055</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4541,19 +4372,14 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119678602</v>
+        <v>119678685</v>
       </c>
       <c r="B38" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -4584,10 +4410,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>476446</v>
+        <v>476473</v>
       </c>
       <c r="R38" t="n">
-        <v>6793039</v>
+        <v>6793064</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4647,49 +4473,36 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119678743</v>
+        <v>119678688</v>
       </c>
       <c r="B39" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
@@ -4698,10 +4511,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>476514</v>
+        <v>476483</v>
       </c>
       <c r="R39" t="n">
-        <v>6793070</v>
+        <v>6793080</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4764,16 +4577,11 @@
         <v>119678764</v>
       </c>
       <c r="B40" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -4867,19 +4675,14 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119678773</v>
+        <v>119678768</v>
       </c>
       <c r="B41" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -4910,10 +4713,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>476572</v>
+        <v>476545</v>
       </c>
       <c r="R41" t="n">
-        <v>6793012</v>
+        <v>6793032</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4970,6 +4773,620 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>119678773</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Unnån-Mysingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>476572</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6793012</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>119678774</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Unnån-Mysingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>476573</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6793014</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>119678775</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Unnån-Mysingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>476576</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6793002</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>119678809</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Unnån-Mysingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>476580</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6793009</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>119678587</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Unnån-Mysingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>476435</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6793012</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>119678589</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Unnån-Mysingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>476438</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6793022</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35570-2024 artfynd.xlsx
+++ b/artfynd/A 35570-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY47"/>
+  <dimension ref="A1:AZ47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119526985</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119527155</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119678608</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1088,6 +1108,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119678679</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119678737</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1306,6 +1336,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119678743</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1418,6 +1453,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119526602</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1530,6 +1570,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119527006</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1642,6 +1687,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119527031</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1743,6 +1793,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119674062</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1844,6 +1899,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119674076</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1945,6 +2005,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119674187</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2046,6 +2111,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119674277</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2147,6 +2217,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119674286</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2248,6 +2323,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119674299</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2349,6 +2429,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119674307</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2450,6 +2535,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119674310</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2551,6 +2641,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119674324</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2652,6 +2747,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119674326</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2753,6 +2853,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119678543</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2854,6 +2959,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119678552</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2955,6 +3065,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119678593</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3056,6 +3171,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119678602</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3157,6 +3277,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119678605</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3258,6 +3383,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119678611</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3359,6 +3489,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119678618</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3460,6 +3595,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119678624</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3561,6 +3701,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119678641</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3662,6 +3807,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119678648</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3763,6 +3913,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119678650</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3864,6 +4019,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119678653</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3965,6 +4125,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119678656</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4066,6 +4231,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119678663</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4167,6 +4337,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119678669</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4268,6 +4443,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119678675</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4369,6 +4549,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119678681</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4470,6 +4655,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119678685</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4571,6 +4761,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119678688</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4672,6 +4867,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119678764</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4773,6 +4973,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119678768</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4874,6 +5079,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119678773</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4975,6 +5185,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119678774</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5076,6 +5291,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119678775</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5177,6 +5397,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119678809</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5282,6 +5507,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119678587</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5387,8 +5617,61 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119678589</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>